--- a/data/trans_orig/P2A_enfcro_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>21441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>12176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22639</t>
+          <t>22974</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>25806</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40281</t>
+          <t>41313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26441</t>
+          <t>26266</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36323</t>
+          <t>36595</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>28190</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39598</t>
+          <t>38988</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58590</t>
+          <t>57558</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73499</t>
+          <t>73065</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21501</t>
+          <t>20981</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34358</t>
+          <t>33962</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25779</t>
+          <t>24687</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38714</t>
+          <t>37235</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48612</t>
+          <t>49590</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67804</t>
+          <t>69347</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33529</t>
+          <t>33925</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>46906</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26220</t>
+          <t>27699</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39155</t>
+          <t>40247</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65016</t>
+          <t>63473</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84208</t>
+          <t>83230</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>62,66%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18281</t>
+          <t>18091</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31123</t>
+          <t>31524</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17187</t>
+          <t>17172</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29831</t>
+          <t>29759</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39219</t>
+          <t>39110</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56906</t>
+          <t>56934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33574</t>
+          <t>33173</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46416</t>
+          <t>46606</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38071</t>
+          <t>38143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50715</t>
+          <t>50730</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75694</t>
+          <t>75666</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93381</t>
+          <t>93490</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,51%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>24778</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37588</t>
+          <t>37314</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30711</t>
+          <t>31062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44389</t>
+          <t>45179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59727</t>
+          <t>60455</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78813</t>
+          <t>78841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,49%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28466</t>
+          <t>28740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41711</t>
+          <t>41276</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29127</t>
+          <t>28337</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42805</t>
+          <t>42454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60756</t>
+          <t>60728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79842</t>
+          <t>79114</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>56,68%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,45%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12129</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22562</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16587</t>
+          <t>16926</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27965</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31650</t>
+          <t>31405</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46452</t>
+          <t>46776</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,28%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24097</t>
+          <t>24269</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34530</t>
+          <t>35261</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24306</t>
+          <t>24771</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35684</t>
+          <t>35345</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52477</t>
+          <t>52153</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67279</t>
+          <t>67524</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31929</t>
+          <t>32248</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47998</t>
+          <t>48809</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38026</t>
+          <t>38220</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55194</t>
+          <t>53763</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74194</t>
+          <t>74439</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98201</t>
+          <t>97666</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,11%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62648</t>
+          <t>61837</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>78717</t>
+          <t>78398</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>55592</t>
+          <t>57023</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>72760</t>
+          <t>72566</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>123232</t>
+          <t>123767</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>147239</t>
+          <t>146994</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,38%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31021</t>
+          <t>30775</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45784</t>
+          <t>45239</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37356</t>
+          <t>37200</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51979</t>
+          <t>52240</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>71409</t>
+          <t>71628</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>93465</t>
+          <t>93125</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>49,87%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44383</t>
+          <t>44928</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59146</t>
+          <t>59392</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44598</t>
+          <t>44337</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59221</t>
+          <t>59377</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>93280</t>
+          <t>93620</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>115336</t>
+          <t>115117</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,64%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>182877</t>
+          <t>181145</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>216941</t>
+          <t>217000</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>208567</t>
+          <t>208778</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>243856</t>
+          <t>245146</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>401501</t>
+          <t>399580</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>451997</t>
+          <t>453282</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>286418</t>
+          <t>286359</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>320482</t>
+          <t>322214</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>284693</t>
+          <t>283403</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>319982</t>
+          <t>319771</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>579911</t>
+          <t>578626</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>630407</t>
+          <t>632328</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,28%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>12344</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>19457</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14989</t>
+          <t>15421</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25587</t>
+          <t>25320</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29766</t>
+          <t>30258</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43081</t>
+          <t>42831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23091</t>
+          <t>22659</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20357</t>
+          <t>20607</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33672</t>
+          <t>33180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,3%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18081</t>
+          <t>17730</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29700</t>
+          <t>29659</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20196</t>
+          <t>19989</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31800</t>
+          <t>32299</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41845</t>
+          <t>40575</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58268</t>
+          <t>58354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,52%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24686</t>
+          <t>24727</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36305</t>
+          <t>36656</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27086</t>
+          <t>26587</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38690</t>
+          <t>38897</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55004</t>
+          <t>54918</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71427</t>
+          <t>72697</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>64,18%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>20108</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32698</t>
+          <t>32196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20635</t>
+          <t>21432</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33485</t>
+          <t>33598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44251</t>
+          <t>43719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62297</t>
+          <t>62046</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>20517</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32163</t>
+          <t>32605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26449</t>
+          <t>26336</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39299</t>
+          <t>38502</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50350</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68396</t>
+          <t>68928</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>61,19%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17611</t>
+          <t>18162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29585</t>
+          <t>30085</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21429</t>
+          <t>20790</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34259</t>
+          <t>34112</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>43129</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59869</t>
+          <t>61985</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>58,95%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20095</t>
+          <t>19595</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32069</t>
+          <t>31518</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21213</t>
+          <t>21360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34043</t>
+          <t>34682</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45283</t>
+          <t>43167</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62111</t>
+          <t>62023</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,98%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>16484</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28274</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>64,9%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>14976</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25602</t>
+          <t>26375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>17496</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28943</t>
+          <t>29002</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23121</t>
+          <t>23292</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34527</t>
+          <t>35030</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44703</t>
+          <t>44884</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60778</t>
+          <t>60414</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,22%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>15540</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26256</t>
+          <t>27046</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26412</t>
+          <t>26241</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33297</t>
+          <t>33661</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49372</t>
+          <t>49191</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,29%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53819</t>
+          <t>53599</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72324</t>
+          <t>71839</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56295</t>
+          <t>56918</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75396</t>
+          <t>75271</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>116158</t>
+          <t>115138</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142235</t>
+          <t>140695</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,0%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44380</t>
+          <t>44865</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62885</t>
+          <t>63105</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>46381</t>
+          <t>46506</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>65482</t>
+          <t>64859</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>96245</t>
+          <t>97785</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>122322</t>
+          <t>123342</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28523</t>
+          <t>28628</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44470</t>
+          <t>44874</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41407</t>
+          <t>41164</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59872</t>
+          <t>59033</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74959</t>
+          <t>74482</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>98930</t>
+          <t>98492</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71069</t>
+          <t>70665</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>87016</t>
+          <t>86911</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70596</t>
+          <t>71435</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>89061</t>
+          <t>89304</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>147077</t>
+          <t>147515</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>171048</t>
+          <t>171525</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>205564</t>
+          <t>204644</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>239769</t>
+          <t>239956</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>239227</t>
+          <t>240217</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>276099</t>
+          <t>278303</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>454290</t>
+          <t>454476</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>509320</t>
+          <t>506927</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>237196</t>
+          <t>237009</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>271401</t>
+          <t>272321</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>262682</t>
+          <t>260478</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>299554</t>
+          <t>298564</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>506426</t>
+          <t>508819</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>561456</t>
+          <t>561270</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,26%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>17995</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28913</t>
+          <t>28700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>23259</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35576</t>
+          <t>34806</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44595</t>
+          <t>44640</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60905</t>
+          <t>61295</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,94%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>16686</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26994</t>
+          <t>27391</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16418</t>
+          <t>17188</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28701</t>
+          <t>28735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36475</t>
+          <t>36085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52785</t>
+          <t>52740</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,16%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32069</t>
+          <t>31559</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45529</t>
+          <t>45867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28863</t>
+          <t>29500</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43941</t>
+          <t>43971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64523</t>
+          <t>66081</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85042</t>
+          <t>85126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,49%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25173</t>
+          <t>24835</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>39143</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36054</t>
+          <t>36024</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51132</t>
+          <t>50495</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65655</t>
+          <t>65571</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>86174</t>
+          <t>84616</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>56,15%</t>
         </is>
       </c>
     </row>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16769</t>
+          <t>16142</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19335</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32319</t>
+          <t>31400</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38740</t>
+          <t>37699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56528</t>
+          <t>56814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t>41971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33858</t>
+          <t>34777</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46842</t>
+          <t>47330</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67761</t>
+          <t>67475</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85549</t>
+          <t>86590</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,67%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20144</t>
+          <t>20569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31908</t>
+          <t>31500</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18429</t>
+          <t>18427</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30170</t>
+          <t>30627</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42575</t>
+          <t>42300</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58621</t>
+          <t>58539</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,11%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13205</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24969</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17480</t>
+          <t>17023</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29221</t>
+          <t>29223</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34142</t>
+          <t>34224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50188</t>
+          <t>50463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,4%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19263</t>
+          <t>19837</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19086</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23082</t>
+          <t>22853</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36545</t>
+          <t>36181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,29%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>12538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22232</t>
+          <t>21342</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16430</t>
+          <t>16156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25617</t>
+          <t>25753</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31345</t>
+          <t>31709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44808</t>
+          <t>45037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,34%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15349</t>
+          <t>15631</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15100</t>
+          <t>15103</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26970</t>
+          <t>27338</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,62%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11934</t>
+          <t>11652</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>19946</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>16253</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25493</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31669</t>
+          <t>31301</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44039</t>
+          <t>42965</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28515</t>
+          <t>28257</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44462</t>
+          <t>45175</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32635</t>
+          <t>32538</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49591</t>
+          <t>50844</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65615</t>
+          <t>65596</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88720</t>
+          <t>88743</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>72303</t>
+          <t>71590</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>88250</t>
+          <t>88508</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>69532</t>
+          <t>68279</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>86488</t>
+          <t>86585</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>147168</t>
+          <t>147145</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>170273</t>
+          <t>170292</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40803</t>
+          <t>41132</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58416</t>
+          <t>58115</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45208</t>
+          <t>46587</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63752</t>
+          <t>65097</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>91635</t>
+          <t>93057</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>115686</t>
+          <t>117378</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,66%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71237</t>
+          <t>71538</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>88850</t>
+          <t>88521</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>75471</t>
+          <t>74126</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94015</t>
+          <t>92636</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>153190</t>
+          <t>151498</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>177241</t>
+          <t>175819</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,39%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>205187</t>
+          <t>206228</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>245939</t>
+          <t>241106</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>216460</t>
+          <t>214222</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>254440</t>
+          <t>253416</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>429534</t>
+          <t>430455</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>483422</t>
+          <t>483498</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>279451</t>
+          <t>284284</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>320203</t>
+          <t>319162</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>316593</t>
+          <t>317617</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>354573</t>
+          <t>356811</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>613001</t>
+          <t>612925</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>666889</t>
+          <t>665968</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,74%</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70112</t>
+          <t>69592</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76828</t>
+          <t>76848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>148255</t>
+          <t>147814</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11045,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>122778</t>
+          <t>122864</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -11060,82 +11060,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>96,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>119098</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>111407</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>123332</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>93,34%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>87,31%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>96,66%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>245511</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>237958</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>250132</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>96,18%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>119098</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>111525</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>123190</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>93,34%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>87,4%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>96,55%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>245511</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>237554</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>250335</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11178,77 +11178,77 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>8498</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4264</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>16189</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6,66%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>9739</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>5118</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>17292</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>3,82%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>8498</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>4406</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>16071</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>6,66%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>12,6%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>9739</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>4915</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>17696</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52121</t>
+          <t>52519</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57611</t>
+          <t>57625</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63489</t>
+          <t>63450</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117926</t>
+          <t>118298</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124133</t>
+          <t>124216</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61781</t>
+          <t>61753</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68863</t>
+          <t>68881</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65890</t>
+          <t>66085</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76902</t>
+          <t>76740</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132147</t>
+          <t>132856</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>144420</t>
+          <t>144578</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16131</t>
+          <t>15422</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33253</t>
+          <t>32739</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65767</t>
+          <t>66971</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -12227,7 +12227,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9465</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38647</t>
+          <t>38736</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>44794</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50401</t>
+          <t>49882</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55205</t>
+          <t>55097</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>91483</t>
+          <t>90719</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>98918</t>
+          <t>98850</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10870</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>112847</t>
+          <t>113999</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>121689</t>
+          <t>121610</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>143131</t>
+          <t>143244</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>152681</t>
+          <t>153043</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>260379</t>
+          <t>260160</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>272902</t>
+          <t>272901</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11661</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12881</t>
+          <t>12768</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>20360</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>108367</t>
+          <t>108963</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>121997</t>
+          <t>122317</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>135818</t>
+          <t>136125</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>148931</t>
+          <t>148443</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>250886</t>
+          <t>249002</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>268150</t>
+          <t>267589</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23252</t>
+          <t>22656</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20977</t>
+          <t>20670</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20264</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37528</t>
+          <t>39412</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>623857</t>
+          <t>624388</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>643158</t>
+          <t>642736</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>708305</t>
+          <t>709120</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>732249</t>
+          <t>732502</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1339500</t>
+          <t>1340125</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1368932</t>
+          <t>1370764</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22997</t>
+          <t>23419</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42298</t>
+          <t>41767</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29723</t>
+          <t>29470</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>53667</t>
+          <t>52852</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>59195</t>
+          <t>57363</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>88627</t>
+          <t>88002</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
